--- a/must_be_sent_to_parse/systems.xlsx
+++ b/must_be_sent_to_parse/systems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heidar\Documents\GitHub\RCM_data_concatinating\must_be_sent_to_parse\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h.alavi\Documents\GitHub\RCM_data_concatinating\must_be_sent_to_parse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A572E1-A6F3-472E-8A59-BE876CA30CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDDC904-5BCB-4F7C-80E9-7686ABDBB452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A3938C61-B607-447E-AF9D-9A7BA19DE119}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{A3938C61-B607-447E-AF9D-9A7BA19DE119}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2322" uniqueCount="1151">
   <si>
     <t>کد سیستم</t>
   </si>
@@ -3484,6 +3484,9 @@
   </si>
   <si>
     <t>SERVER.IT</t>
+  </si>
+  <si>
+    <t>Monitoring Room</t>
   </si>
 </sst>
 </file>
@@ -3812,13 +3815,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
@@ -3839,6 +3835,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3948,7 +3951,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B49871C7-9D25-4CA7-95C1-DB4B1D9DF521}" name="Table2" displayName="Table2" ref="A1:G1071" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B49871C7-9D25-4CA7-95C1-DB4B1D9DF521}" name="Table2" displayName="Table2" ref="A1:G1071" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7">
   <autoFilter ref="A1:G1071" xr:uid="{B49871C7-9D25-4CA7-95C1-DB4B1D9DF521}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1FD1B96C-2E48-4E59-AD1D-9AF17A4B81AD}" name="کد سیستم" dataDxfId="6"/>
@@ -23773,7 +23776,7 @@
         <v>1113</v>
       </c>
       <c r="B1035" s="14" t="str">
-        <f t="shared" ref="B1035:B1069" si="30">A1035</f>
+        <f t="shared" ref="B1035:B1068" si="30">A1035</f>
         <v>ER011S01</v>
       </c>
       <c r="C1035" s="10" t="s">
@@ -23781,7 +23784,7 @@
       </c>
       <c r="D1035" s="15"/>
       <c r="E1035" s="15" t="str">
-        <f t="shared" ref="E1035:E1045" si="31">VLOOKUP(LEFT(A1035,4),$A$2:$B$73,2,FALSE)</f>
+        <f t="shared" ref="E1035:E1044" si="31">VLOOKUP(LEFT(A1035,4),$A$2:$B$73,2,FALSE)</f>
         <v>Electric Room 1</v>
       </c>
       <c r="F1035" s="15"/>
@@ -24390,7 +24393,7 @@
         <v>1147</v>
       </c>
       <c r="B1069" s="16" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="C1069" s="10" t="s">
         <v>13</v>
